--- a/artfynd/A 48937-2021 artfynd.xlsx
+++ b/artfynd/A 48937-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48937-2021 artfynd.xlsx
+++ b/artfynd/A 48937-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96720187</v>
+        <v>96714337</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,23 +703,30 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skallerbacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520057.6826608463</v>
+        <v>520031</v>
       </c>
       <c r="R2" t="n">
-        <v>6702079.189962224</v>
+        <v>6702097</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +774,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96720198</v>
+        <v>96720187</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520161.2215174185</v>
+        <v>520058</v>
       </c>
       <c r="R3" t="n">
-        <v>6702033.387287268</v>
+        <v>6702079</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +863,9 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,64 +893,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96717106</v>
+        <v>96720198</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skallerbacken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520122.0092424128</v>
+        <v>520161</v>
       </c>
       <c r="R4" t="n">
-        <v>6702064.252063675</v>
+        <v>6702034</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,32 +964,18 @@
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Minst 6-7 plantor.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1035,63 +994,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96714337</v>
+        <v>102069167</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skallerbacken, Dlr</t>
+          <t>Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520030.4053092922</v>
+        <v>519976</v>
       </c>
       <c r="R5" t="n">
-        <v>6702096.800436137</v>
+        <v>6702133</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,22 +1066,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-18</t>
+          <t>2022-07-05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,59 +1096,59 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102069161</v>
+        <v>102068505</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1207,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519981.2681090751</v>
+        <v>520107</v>
       </c>
       <c r="R6" t="n">
-        <v>6702135.505167651</v>
+        <v>6702023</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,6 +1227,368 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102068590</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>520111</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6702019</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96717106</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skallerbacken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>520123</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702064</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 6-7 plantor.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102069161</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>519981</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6702136</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48937-2021 artfynd.xlsx
+++ b/artfynd/A 48937-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714337</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96720187</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96720198</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102069167</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102068505</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102068590</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96717106</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,8 +1629,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102069161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>